--- a/results/df_reproduced.xlsx
+++ b/results/df_reproduced.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,47 +441,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>num_students</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>BoW.silhouette_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>BoW.balance_score</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>BoW.labels</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>embeddings.silhouette_score</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>embeddings.davies_bouldin</t>
+        </is>
+      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>embeddings.balance_score</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>embeddings.labels</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>num_students</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>num_edges</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>avg_degree</t>
+          <t>embeddings.calinski_harabasz</t>
         </is>
       </c>
     </row>
@@ -493,35 +473,17 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09899495384260193</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 0, 0, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 1, 0, 1, 1, 0, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 1]</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>0.5516940951347351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6003534197807312</v>
+        <v>0.6120839902186083</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8409090909090909</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[0, 1, 0, 0, 1, 1, 0, 0, 0, 1, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 1, 1, 0, 1, 1, 1, 0, 1, 1, 0, 0, 0, 1, 1, 1, 0, 0, 1, 0, 1, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>74</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2701</v>
-      </c>
-      <c r="K2" t="n">
-        <v>73</v>
+        <v>119.8634719862007</v>
       </c>
     </row>
     <row r="3">
@@ -532,35 +494,17 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.09899495384260193</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 0, 0, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 1, 0, 1, 1, 0, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 1]</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.5862144827842712</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5841408371925354</v>
+        <v>0.5328837778025122</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8809523809523809</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 0, 0, 1, 1, 1, 1, 1, 1, 0, 0, 1, 0, 0, 1, 1, 0, 1, 0, 1, 1, 1, 1, 1, 0, 0, 0, 1, 1, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 0, 0, 1, 1, 1, 0, 1, 1, 0, 1, 0, 0, 1, 0, 0]</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>74</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2701</v>
-      </c>
-      <c r="K3" t="n">
-        <v>73</v>
+        <v>137.7623666627406</v>
       </c>
     </row>
     <row r="4">
@@ -571,35 +515,17 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09899495384260193</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 0, 0, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 1, 0, 1, 1, 0, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 1]</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.3521806597709656</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3441871702671051</v>
+        <v>1.112261973975185</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7708333333333334</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 0, 1, 0, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 0, 0, 0, 1, 1, 0, 0, 1, 1, 0, 1, 1, 0, 1, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>74</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2701</v>
-      </c>
-      <c r="K4" t="n">
-        <v>73</v>
+        <v>46.04822672040007</v>
       </c>
     </row>
     <row r="5">
@@ -610,35 +536,17 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09899495384260193</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 0, 0, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 1, 0, 1, 1, 0, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 1]</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0.1970214396715164</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1789070516824722</v>
+        <v>1.822792323398177</v>
       </c>
       <c r="G5" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 0, 1, 1, 1, 1, 0, 0, 0, 1, 0, 1, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 1, 1, 1, 0, 1, 0, 1, 0, 1, 1, 1, 0, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 0, 1, 0, 1, 1, 1, 1, 0, 0, 0, 0, 1, 0, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>74</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2701</v>
-      </c>
-      <c r="K5" t="n">
-        <v>73</v>
+        <v>18.3514227943611</v>
       </c>
     </row>
     <row r="6">
@@ -649,35 +557,17 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09899495384260193</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9024390243902439</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 0, 0, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 1, 0, 1, 1, 0, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 1]</t>
-        </is>
+        <v>74</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.08401197195053101</v>
       </c>
       <c r="F6" t="n">
-        <v>0.109139621257782</v>
+        <v>2.79553495650467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[0, 0, 1, 1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 0, 1, 0, 0, 0, 1, 0, 1, 1, 0, 1, 1, 0, 1, 1, 1, 0, 0, 0, 0, 1, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 0, 0, 1, 1, 1, 1, 0, 0, 0, 1, 0, 0, 0, 0, 1, 0, 1, 1, 0, 1, 1, 0, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>74</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2701</v>
-      </c>
-      <c r="K6" t="n">
-        <v>73</v>
+        <v>7.735730457866455</v>
       </c>
     </row>
     <row r="7">
@@ -688,35 +578,17 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2312577773387333</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.5828758478164673</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6215593218803406</v>
+        <v>0.5117183987237901</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7285714285714285</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 1, 1, 1, 1, 0, 0, 1, 1, 1, 1, 0, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 0, 0, 1, 0, 0, 1, 1, 1, 1, 0, 0, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>51</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1275</v>
-      </c>
-      <c r="K7" t="n">
-        <v>50</v>
+        <v>98.79504062927408</v>
       </c>
     </row>
     <row r="8">
@@ -727,35 +599,17 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2312577773387333</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0.5674307942390442</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6174559593200684</v>
+        <v>0.566440271819975</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9807692307692307</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 1, 1, 1, 1, 0, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 0, 0, 1, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>51</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1275</v>
-      </c>
-      <c r="K8" t="n">
-        <v>50</v>
+        <v>92.70062338610398</v>
       </c>
     </row>
     <row r="9">
@@ -766,35 +620,17 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2312577773387333</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.3939523100852966</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3334551155567169</v>
+        <v>0.9454592363260914</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 1, 1, 0, 1, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 1, 1, 1, 0, 1, 0, 0, 1, 0, 1, 1, 1, 1, 0, 1, 0, 1, 0, 1, 1, 0, 0, 1, 1, 0, 1, 1, 0, 0, 1, 1, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>51</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1275</v>
-      </c>
-      <c r="K9" t="n">
-        <v>50</v>
+        <v>44.13870489378308</v>
       </c>
     </row>
     <row r="10">
@@ -805,35 +641,17 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2312577773387333</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>0.2026121914386749</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2383506745100021</v>
+        <v>1.761729113929103</v>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 0, 1, 1, 0, 1, 0, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 1, 0, 0, 1, 1, 1, 1, 0, 0, 1, 1, 1, 1, 0, 0, 1, 1, 0, 1, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>51</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1275</v>
-      </c>
-      <c r="K10" t="n">
-        <v>50</v>
+        <v>13.93143757197203</v>
       </c>
     </row>
     <row r="11">
@@ -844,35 +662,17 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2312577773387333</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6375</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>51</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0.09040884673595428</v>
       </c>
       <c r="F11" t="n">
-        <v>0.101054809987545</v>
+        <v>2.746756142112747</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9807692307692307</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[0, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 1, 1, 1, 0, 1, 1, 0, 1, 0, 1, 1, 1, 1, 0, 0, 1, 0, 0, 1, 0, 1, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>51</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1275</v>
-      </c>
-      <c r="K11" t="n">
-        <v>50</v>
+        <v>6.124904141547804</v>
       </c>
     </row>
     <row r="12">
@@ -883,35 +683,17 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1421446230393624</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>[1, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0.5509580969810486</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5708792805671692</v>
+        <v>0.5826709099203532</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7741935483870968</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 1, 0, 1, 0, 1, 0, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0, 0, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1128</v>
-      </c>
-      <c r="K12" t="n">
-        <v>47</v>
+        <v>90.13345407866979</v>
       </c>
     </row>
     <row r="13">
@@ -922,35 +704,17 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1421446230393624</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[1, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0.5507810115814209</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5856649875640869</v>
+        <v>0.6371557872062439</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8275862068965517</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 1, 1, 1, 0, 1, 1, 1, 0, 1, 1, 0, 1, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 0, 1, 0, 1, 0, 1, 0, 1, 1, 1, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>48</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1128</v>
-      </c>
-      <c r="K13" t="n">
-        <v>47</v>
+        <v>81.03346512974771</v>
       </c>
     </row>
     <row r="14">
@@ -961,35 +725,17 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1421446230393624</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[1, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0.3716130256652832</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3771696090698242</v>
+        <v>1.051408522158665</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7741935483870968</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>[0, 0, 1, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 1, 0, 0, 0, 1, 1, 0, 1, 1, 1, 1, 0, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>48</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1128</v>
-      </c>
-      <c r="K14" t="n">
-        <v>47</v>
+        <v>32.72311447791857</v>
       </c>
     </row>
     <row r="15">
@@ -1000,35 +746,17 @@
         <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1421446230393624</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>[1, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0.2143531292676926</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1984717100858688</v>
+        <v>1.543749203101209</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 0, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>48</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1128</v>
-      </c>
-      <c r="K15" t="n">
-        <v>47</v>
+        <v>12.02072739901513</v>
       </c>
     </row>
     <row r="16">
@@ -1039,35 +767,17 @@
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1421446230393624</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>[1, 0, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0]</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0.07548551261425018</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1193166598677635</v>
+        <v>2.95234687246526</v>
       </c>
       <c r="G16" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 1, 0, 1, 0, 1, 1, 1, 1, 1, 1, 0, 0, 1, 1, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>48</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1128</v>
-      </c>
-      <c r="K16" t="n">
-        <v>47</v>
+        <v>5.052531675916581</v>
       </c>
     </row>
     <row r="17">
@@ -1078,35 +788,17 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.127990835889721</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.7903225806451613</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 1, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>0.5544628500938416</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6065243482589722</v>
+        <v>0.5929192769720422</v>
       </c>
       <c r="G17" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[0, 1, 1, 1, 0, 0, 1, 1, 1, 1, 0, 1, 0, 0, 0, 1, 1, 0, 0, 0, 0, 1, 0, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 1, 0, 1, 1, 1, 0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>49</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1176</v>
-      </c>
-      <c r="K17" t="n">
-        <v>48</v>
+        <v>67.92690352595729</v>
       </c>
     </row>
     <row r="18">
@@ -1117,35 +809,17 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.127990835889721</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.7903225806451613</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 1, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>0.5601266622543335</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5947739481925964</v>
+        <v>0.5995029744873289</v>
       </c>
       <c r="G18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 1, 1, 1, 1, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>49</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1176</v>
-      </c>
-      <c r="K18" t="n">
-        <v>48</v>
+        <v>79.74916508397752</v>
       </c>
     </row>
     <row r="19">
@@ -1156,35 +830,17 @@
         <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.127990835889721</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.7903225806451613</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 1, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>0.3677866756916046</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3534330725669861</v>
+        <v>0.9838387070018999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9423076923076923</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[0, 1, 1, 0, 0, 1, 0, 0, 0, 1, 1, 1, 1, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 1, 0, 1, 0, 1, 1, 1, 0, 0, 1, 1, 0, 0, 1, 1, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>49</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1176</v>
-      </c>
-      <c r="K19" t="n">
-        <v>48</v>
+        <v>35.65850281574566</v>
       </c>
     </row>
     <row r="20">
@@ -1195,35 +851,17 @@
         <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0.127990835889721</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.7903225806451613</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 1, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>0.2109716534614563</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1945377886295319</v>
+        <v>1.676902125919502</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9423076923076923</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 0, 1, 1, 1, 1, 1, 0, 1, 0, 1, 0, 1, 1, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>49</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1176</v>
-      </c>
-      <c r="K20" t="n">
-        <v>48</v>
+        <v>13.72654669679029</v>
       </c>
     </row>
     <row r="21">
@@ -1234,35 +872,17 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>0.127990835889721</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.7903225806451613</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 1, 0, 1, 0, 1, 1, 0, 1, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0]</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.09136629849672318</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1117050796747208</v>
+        <v>2.729229510274599</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7424242424242424</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 1, 0, 0, 1, 0, 0, 1, 0, 0, 1, 0, 1, 0, 1, 0, 0, 0, 1, 0, 0, 1, 0, 1, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>49</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1176</v>
-      </c>
-      <c r="K21" t="n">
-        <v>48</v>
+        <v>5.952514214512725</v>
       </c>
     </row>
     <row r="22">
@@ -1273,35 +893,17 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1164724725352648</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1]</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>0.5409384965896606</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5803514719009399</v>
+        <v>0.6366628080886721</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 0, 0, 0, 1, 1, 1, 1, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>52</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1326</v>
-      </c>
-      <c r="K22" t="n">
-        <v>51</v>
+        <v>80.08232427405765</v>
       </c>
     </row>
     <row r="23">
@@ -1312,35 +914,17 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1164724725352648</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1]</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>0.6120653748512268</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6571824550628662</v>
+        <v>0.5298505494860984</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>[0, 1, 0, 0, 1, 1, 0, 0, 1, 0, 0, 1, 0, 0, 1, 1, 0, 0, 1, 1, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 0, 1, 1, 0, 1, 1, 0, 0, 1, 0, 0, 1, 1, 0, 0, 0, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>52</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1326</v>
-      </c>
-      <c r="K23" t="n">
-        <v>51</v>
+        <v>126.99692847176</v>
       </c>
     </row>
     <row r="24">
@@ -1351,35 +935,17 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1164724725352648</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1]</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>0.3702130019664764</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3779312670230865</v>
+        <v>1.019536313324441</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 1, 1, 0, 1, 0, 1, 1, 0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 1, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 0, 0, 0, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>52</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1326</v>
-      </c>
-      <c r="K24" t="n">
-        <v>51</v>
+        <v>37.94014721812151</v>
       </c>
     </row>
     <row r="25">
@@ -1390,35 +956,17 @@
         <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1164724725352648</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1]</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>0.2005992829799652</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2174770832061768</v>
+        <v>1.622150302767779</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9629629629629629</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 1, 1, 1, 0, 0, 1, 1, 1, 1, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 0, 0, 1, 1, 1, 0, 0, 1, 1, 1, 0, 1, 1, 0, 0, 0, 1, 0, 0, 0, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>52</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1326</v>
-      </c>
-      <c r="K25" t="n">
-        <v>51</v>
+        <v>13.51890235298687</v>
       </c>
     </row>
     <row r="26">
@@ -1429,35 +977,17 @@
         <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1164724725352648</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 0, 1, 1, 1, 1]</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0.09183018654584885</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1229644194245338</v>
+        <v>2.830482559948361</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8387096774193549</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>[0, 0, 0, 1, 0, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 1, 0, 0, 1, 1, 1, 0, 1, 1, 1, 0, 0, 1, 1, 0, 0, 1, 0, 1, 0, 0, 1, 1, 1, 1, 1, 0, 0, 0, 0]</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>52</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1326</v>
-      </c>
-      <c r="K26" t="n">
-        <v>51</v>
+        <v>5.540668900400562</v>
       </c>
     </row>
     <row r="27">
@@ -1468,35 +998,17 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2024554776850852</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.7790697674418605</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.5302903652191162</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5504984259605408</v>
+        <v>0.6218084684452329</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8589743589743589</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[1, 0, 1, 0, 0, 1, 0, 1, 1, 1, 1, 0, 1, 1, 0, 0, 0, 1, 1, 1, 0, 1, 0, 0, 0, 0, 1, 0, 1, 0, 0, 1, 1, 0, 1, 0, 0, 0, 1, 0, 0, 1, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 1, 1, 0, 1, 0, 1, 0, 0, 0, 0, 1, 0, 1, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>67</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2211</v>
-      </c>
-      <c r="K27" t="n">
-        <v>66</v>
+        <v>114.2790972658938</v>
       </c>
     </row>
     <row r="28">
@@ -1507,35 +1019,17 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2024554776850852</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.7790697674418605</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.5969101786613464</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5827755928039551</v>
+        <v>0.5157862164031713</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8375</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 0, 1, 0, 1, 1, 1, 1, 0, 0, 0, 0, 0, 0, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 0, 1, 0, 1, 1, 1, 1, 0, 0, 0, 1, 1, 1, 1, 1, 1, 1, 0, 1, 0, 0, 0, 1, 0, 0, 1, 1, 0, 1, 0, 1, 0, 1, 1, 1, 1, 0, 1]</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>67</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2211</v>
-      </c>
-      <c r="K28" t="n">
-        <v>66</v>
+        <v>121.557660670731</v>
       </c>
     </row>
     <row r="29">
@@ -1546,35 +1040,17 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2024554776850852</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.7790697674418605</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0.4076817631721497</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3602640628814697</v>
+        <v>0.9517294129766507</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7976190476190477</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 1, 0, 0, 0, 1, 0, 1, 0, 0, 1, 0, 1, 0, 1, 1, 0, 0, 1, 0, 0, 1, 0, 0, 1, 0, 0, 0, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 1, 1, 0, 0, 1, 0, 0, 1, 0, 0, 1, 0, 0, 0, 0, 0, 0, 1, 1, 0, 0, 1, 0, 0, 1, 1, 0]</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>67</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2211</v>
-      </c>
-      <c r="K29" t="n">
-        <v>66</v>
+        <v>43.36120116524181</v>
       </c>
     </row>
     <row r="30">
@@ -1585,35 +1061,17 @@
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2024554776850852</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.7790697674418605</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0.2000452429056168</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1930155456066132</v>
+        <v>1.815778724861675</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9305555555555556</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[1, 1, 1, 0, 1, 0, 0, 1, 1, 1, 1, 0, 0, 0, 0, 1, 1, 1, 0, 0, 0, 1, 0, 0, 0, 0, 1, 1, 1, 0, 0, 1, 1, 1, 0, 0, 0, 0, 0, 0, 1, 0, 1, 0, 0, 0, 0, 1, 0, 0, 0, 0, 0, 0, 0, 1, 1, 1, 0, 1, 0, 1, 1, 1, 1, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>67</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2211</v>
-      </c>
-      <c r="K30" t="n">
-        <v>66</v>
+        <v>17.8116195181385</v>
       </c>
     </row>
     <row r="31">
@@ -1624,35 +1082,17 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2024554776850852</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.7790697674418605</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>[1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 1, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0, 0]</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>0.09273211658000946</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1107316687703133</v>
+        <v>2.739283937992121</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9054054054054054</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[1, 1, 0, 1, 0, 0, 0, 1, 1, 1, 0, 0, 1, 1, 1, 1, 0, 1, 1, 0, 1, 0, 1, 1, 1, 1, 0, 0, 0, 1, 1, 1, 0, 0, 1, 1, 0, 1, 1, 1, 0, 1, 0, 1, 1, 0, 0, 0, 0, 0, 0, 0, 1, 0, 1, 1, 1, 1, 0, 0, 1, 1, 0, 0, 0, 1, 1]</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>67</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2211</v>
-      </c>
-      <c r="K31" t="n">
-        <v>66</v>
+        <v>7.480434196175196</v>
       </c>
     </row>
   </sheetData>
